--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136760016</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759800</v>
       </c>
       <c r="B6" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136760018</v>
       </c>
       <c r="B7" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136760017</v>
       </c>
       <c r="B8" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38431-2026 artfynd.xlsx
+++ b/artfynd/A 38431-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760014</v>
       </c>
       <c r="B2" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136760015</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136760013</v>
       </c>
       <c r="B4" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
